--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98024</v>
+        <v>98030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98030</v>
+        <v>98042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98042</v>
+        <v>98043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98043</v>
+        <v>98046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2026 artfynd.xlsx
+++ b/artfynd/A 37817-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137301445</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305201</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
